--- a/research/traditional_assets/database/data/brazil/brazil_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,116 +587,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D2">
+        <v>1.565</v>
+      </c>
+      <c r="E2">
+        <v>-0.278755</v>
+      </c>
       <c r="G2">
-        <v>0.3279168858495529</v>
+        <v>0.2957854774376472</v>
       </c>
       <c r="H2">
-        <v>0.291951604418727</v>
+        <v>0.2516699505021865</v>
       </c>
       <c r="I2">
-        <v>0.2791688584955286</v>
+        <v>0.1658417031092316</v>
       </c>
       <c r="J2">
-        <v>0.2375075677983622</v>
+        <v>0.1331549172322448</v>
       </c>
       <c r="K2">
-        <v>39.98999999999999</v>
+        <v>41.07000000000001</v>
       </c>
       <c r="L2">
-        <v>0.2103629668595476</v>
+        <v>0.197366524100149</v>
       </c>
       <c r="M2">
-        <v>50.82</v>
+        <v>70</v>
       </c>
       <c r="N2">
-        <v>0.06815073085691296</v>
+        <v>0.07892036934732855</v>
       </c>
       <c r="O2">
-        <v>1.270817704426107</v>
+        <v>1.704407109812515</v>
       </c>
       <c r="P2">
-        <v>46.4</v>
+        <v>55.90000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.06222341424165213</v>
+        <v>0.06302355209308094</v>
       </c>
       <c r="R2">
-        <v>1.16029007251813</v>
+        <v>1.36109082055028</v>
       </c>
       <c r="S2">
-        <v>4.420000000000002</v>
+        <v>14.1</v>
       </c>
       <c r="T2">
-        <v>0.08697363242817792</v>
+        <v>0.2014285714285715</v>
       </c>
       <c r="U2">
-        <v>42.42</v>
+        <v>29.547</v>
       </c>
       <c r="V2">
-        <v>0.05688614724420008</v>
+        <v>0.03331228790150738</v>
       </c>
       <c r="W2">
-        <v>0.3811764705882353</v>
+        <v>0.05925925925925925</v>
       </c>
       <c r="X2">
-        <v>0.07095281200951604</v>
+        <v>0.106024237166538</v>
       </c>
       <c r="Y2">
-        <v>0.3102236585787193</v>
+        <v>-0.04676497790727877</v>
       </c>
       <c r="Z2">
-        <v>3.946439692754827</v>
+        <v>0.6045279313460326</v>
       </c>
       <c r="AA2">
-        <v>1.501780384892456</v>
+        <v>0.03451077701552085</v>
       </c>
       <c r="AB2">
-        <v>0.06600686796671337</v>
+        <v>0.1020323325789546</v>
       </c>
       <c r="AC2">
-        <v>1.436382262010654</v>
+        <v>-0.06759379037281943</v>
       </c>
       <c r="AD2">
-        <v>66.59999999999999</v>
+        <v>135.352</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>66.59999999999999</v>
+        <v>135.352</v>
       </c>
       <c r="AG2">
-        <v>24.17999999999999</v>
+        <v>105.805</v>
       </c>
       <c r="AH2">
-        <v>0.08198941277853009</v>
+        <v>0.1323966421538419</v>
       </c>
       <c r="AI2">
-        <v>0.1737995824634656</v>
+        <v>0.2957272576317698</v>
       </c>
       <c r="AJ2">
-        <v>0.03140749207668727</v>
+        <v>0.1065750044068394</v>
       </c>
       <c r="AK2">
-        <v>0.07095486824344151</v>
+        <v>0.2471242219341578</v>
       </c>
       <c r="AL2">
-        <v>5.65</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AM2">
-        <v>4.132000000000001</v>
+        <v>8.202</v>
       </c>
       <c r="AN2">
-        <v>1.15625</v>
+        <v>3.711120859837683</v>
       </c>
       <c r="AO2">
-        <v>9.3929203539823</v>
+        <v>3.651851851851852</v>
       </c>
       <c r="AP2">
-        <v>0.4197916666666665</v>
+        <v>2.900992542224172</v>
       </c>
       <c r="AQ2">
-        <v>12.84365924491771</v>
+        <v>4.207510363326018</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bahema Educação S.A. (BOVESPA:BAHI3)</t>
+          <t>Vinci Partners Investments Ltd. (NasdaqGS:VINP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,112 +722,115 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.2026258205689278</v>
+        <v>0.5791458607095927</v>
       </c>
       <c r="H3">
-        <v>0.2026258205689278</v>
+        <v>0.5795006570302235</v>
       </c>
       <c r="I3">
-        <v>0.02910284463894967</v>
+        <v>0.4467805519053877</v>
       </c>
       <c r="J3">
-        <v>0.02910284463894967</v>
+        <v>0.3709940161379655</v>
       </c>
       <c r="K3">
-        <v>-4.79</v>
+        <v>40.2</v>
       </c>
       <c r="L3">
-        <v>-0.1048140043763676</v>
+        <v>0.5282522996057819</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>51.8</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.1035378772736358</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.288557213930348</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>37.7</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.07535478712772337</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.9378109452736318</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>14.1</v>
+      </c>
+      <c r="T3">
+        <v>0.2722007722007722</v>
       </c>
       <c r="U3">
-        <v>7.22</v>
+        <v>18</v>
       </c>
       <c r="V3">
-        <v>0.1769607843137255</v>
+        <v>0.03597841295222867</v>
       </c>
       <c r="W3">
-        <v>-0.3193333333333334</v>
+        <v>0.1521574564723694</v>
       </c>
       <c r="X3">
-        <v>0.09022661840010969</v>
+        <v>0.106024237166538</v>
       </c>
       <c r="Y3">
-        <v>-0.4095599517334431</v>
+        <v>0.04613321930583142</v>
       </c>
       <c r="Z3">
-        <v>66.23188405797124</v>
+        <v>0.2890239270793771</v>
       </c>
       <c r="AA3">
-        <v>1.927536231884065</v>
+        <v>0.1072261474671446</v>
       </c>
       <c r="AB3">
-        <v>0.06661049933074928</v>
+        <v>0.1020323325789546</v>
       </c>
       <c r="AC3">
-        <v>1.860925732553315</v>
+        <v>0.005193814888190026</v>
       </c>
       <c r="AD3">
-        <v>30.8</v>
+        <v>48.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>30.8</v>
+        <v>48.2</v>
       </c>
       <c r="AG3">
-        <v>23.58</v>
+        <v>30.2</v>
       </c>
       <c r="AH3">
-        <v>0.4301675977653632</v>
+        <v>0.0878760255241568</v>
       </c>
       <c r="AI3">
-        <v>0.5202702702702703</v>
+        <v>0.1586048042119118</v>
       </c>
       <c r="AJ3">
-        <v>0.3662628145386767</v>
+        <v>0.05692742695570217</v>
       </c>
       <c r="AK3">
-        <v>0.4536360138514813</v>
+        <v>0.105631339629241</v>
       </c>
       <c r="AL3">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AM3">
-        <v>1.076</v>
+        <v>2.25</v>
       </c>
       <c r="AN3">
-        <v>6.497890295358649</v>
+        <v>1.389048991354467</v>
       </c>
       <c r="AO3">
-        <v>0.7112299465240641</v>
+        <v>15.11111111111111</v>
       </c>
       <c r="AP3">
-        <v>4.974683544303797</v>
+        <v>0.8703170028818444</v>
       </c>
       <c r="AQ3">
-        <v>1.236059479553903</v>
+        <v>15.11111111111111</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vinci Partners Investments Ltd. (NasdaqGS:VINP)</t>
+          <t>Investimentos Bemge S.A. (BOVESPA:FIGE3)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,116 +849,107 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="E4">
+        <v>0.00049</v>
+      </c>
       <c r="G4">
-        <v>0.5058045292014303</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.5029797377830751</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.5530393325387365</v>
+        <v>0.9266503667481663</v>
       </c>
       <c r="J4">
-        <v>0.440331316666918</v>
+        <v>0.6259168704156479</v>
       </c>
       <c r="K4">
-        <v>38.3</v>
+        <v>2.56</v>
       </c>
       <c r="L4">
-        <v>0.4564958283671036</v>
+        <v>0.6259168704156479</v>
       </c>
       <c r="M4">
-        <v>50.82</v>
+        <v>18.2</v>
       </c>
       <c r="N4">
-        <v>0.0839722405816259</v>
+        <v>2.469470827679783</v>
       </c>
       <c r="O4">
-        <v>1.326892950391645</v>
+        <v>7.109375</v>
       </c>
       <c r="P4">
-        <v>46.4</v>
+        <v>18.2</v>
       </c>
       <c r="Q4">
-        <v>0.07666886979510905</v>
+        <v>2.469470827679783</v>
       </c>
       <c r="R4">
-        <v>1.211488250652742</v>
+        <v>7.109375</v>
       </c>
       <c r="S4">
-        <v>4.420000000000002</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.08697363242817792</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.0322207534699273</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.622881355932203</v>
+        <v>0.05925925925925925</v>
       </c>
       <c r="X4">
-        <v>0.06626052353200959</v>
+        <v>0.1020052760592112</v>
       </c>
       <c r="Y4">
-        <v>1.556620832400194</v>
+        <v>-0.04274601679995191</v>
       </c>
       <c r="Z4">
-        <v>3.410569105691057</v>
+        <v>0.09467592592592591</v>
       </c>
       <c r="AA4">
-        <v>1.501780384892456</v>
+        <v>0.05925925925925925</v>
       </c>
       <c r="AB4">
-        <v>0.06539812288180272</v>
+        <v>0.1020052760592112</v>
       </c>
       <c r="AC4">
-        <v>1.436382262010654</v>
+        <v>-0.04274601679995191</v>
       </c>
       <c r="AD4">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-0.8999999999999986</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>0.02981724911830715</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.06577086280056578</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.001489326493463509</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>-0.003418154196733758</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>2.33</v>
-      </c>
-      <c r="AN4">
-        <v>0.3957446808510638</v>
-      </c>
-      <c r="AO4">
-        <v>19.91416309012875</v>
-      </c>
-      <c r="AP4">
-        <v>-0.01914893617021273</v>
-      </c>
-      <c r="AQ4">
-        <v>19.91416309012875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -968,23 +968,29 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D5">
+        <v>2.467</v>
+      </c>
+      <c r="E5">
+        <v>-0.5579999999999999</v>
+      </c>
       <c r="G5">
-        <v>0.1758677685950413</v>
+        <v>0.2042296072507553</v>
       </c>
       <c r="H5">
-        <v>0.06677685950413223</v>
+        <v>0.06978851963746223</v>
       </c>
       <c r="I5">
-        <v>0.08826446280991736</v>
+        <v>0.02613293051359517</v>
       </c>
       <c r="J5">
-        <v>0.06673654505140093</v>
+        <v>0.01329342619177918</v>
       </c>
       <c r="K5">
-        <v>6.48</v>
+        <v>0.41</v>
       </c>
       <c r="L5">
-        <v>0.1071074380165289</v>
+        <v>0.006193353474320241</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1008,73 +1014,299 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>15.7</v>
+        <v>7.71</v>
       </c>
       <c r="V5">
-        <v>0.1574724172517553</v>
+        <v>0.1683406113537118</v>
       </c>
       <c r="W5">
-        <v>0.3811764705882353</v>
+        <v>0.01708333333333333</v>
       </c>
       <c r="X5">
-        <v>0.07095281200951604</v>
+        <v>0.121861116931262</v>
       </c>
       <c r="Y5">
-        <v>0.3102236585787193</v>
+        <v>-0.1047777835979287</v>
       </c>
       <c r="Z5">
-        <v>2.644230769230769</v>
+        <v>2.596078431372549</v>
       </c>
       <c r="AA5">
-        <v>0.1764668258570697</v>
+        <v>0.03451077701552085</v>
       </c>
       <c r="AB5">
-        <v>0.06600686796671337</v>
+        <v>0.1021045673883403</v>
       </c>
       <c r="AC5">
-        <v>0.1104599578903563</v>
+        <v>-0.06759379037281943</v>
       </c>
       <c r="AD5">
-        <v>17.2</v>
+        <v>21.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>17.2</v>
+        <v>21.8</v>
       </c>
       <c r="AG5">
-        <v>1.5</v>
+        <v>14.09</v>
       </c>
       <c r="AH5">
-        <v>0.1471343028229256</v>
+        <v>0.3224852071005918</v>
       </c>
       <c r="AI5">
-        <v>0.4174757281553398</v>
+        <v>0.4749455337690631</v>
       </c>
       <c r="AJ5">
-        <v>0.01482213438735178</v>
+        <v>0.2352646518617465</v>
       </c>
       <c r="AK5">
-        <v>0.05882352941176471</v>
+        <v>0.3689447499345379</v>
       </c>
       <c r="AL5">
-        <v>1.45</v>
+        <v>2.63</v>
       </c>
       <c r="AM5">
-        <v>0.726</v>
+        <v>1.46</v>
       </c>
       <c r="AN5">
-        <v>2.935153583617747</v>
+        <v>8.257575757575758</v>
       </c>
       <c r="AO5">
-        <v>3.682758620689655</v>
+        <v>0.6577946768060837</v>
       </c>
       <c r="AP5">
-        <v>0.2559726962457338</v>
+        <v>5.337121212121212</v>
       </c>
       <c r="AQ5">
-        <v>7.355371900826446</v>
+        <v>1.184931506849315</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bahema Educação S.A. (BOVESPA:BAHI3)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.6629999999999999</v>
+      </c>
+      <c r="G6">
+        <v>0.06413290113452187</v>
+      </c>
+      <c r="H6">
+        <v>0.05915721231766612</v>
+      </c>
+      <c r="I6">
+        <v>-0.07163695299837924</v>
+      </c>
+      <c r="J6">
+        <v>-0.07163695299837924</v>
+      </c>
+      <c r="K6">
+        <v>-16.9</v>
+      </c>
+      <c r="L6">
+        <v>-0.2739059967585089</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>3.15</v>
+      </c>
+      <c r="V6">
+        <v>0.05311973018549747</v>
+      </c>
+      <c r="W6">
+        <v>-0.6425855513307984</v>
+      </c>
+      <c r="X6">
+        <v>0.1478712025243035</v>
+      </c>
+      <c r="Y6">
+        <v>-0.7904567538551019</v>
+      </c>
+      <c r="Z6">
+        <v>5.107615894039733</v>
+      </c>
+      <c r="AA6">
+        <v>-0.3658940397350992</v>
+      </c>
+      <c r="AB6">
+        <v>0.102166518651217</v>
+      </c>
+      <c r="AC6">
+        <v>-0.4680605583863162</v>
+      </c>
+      <c r="AD6">
+        <v>65.2</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>65.2</v>
+      </c>
+      <c r="AG6">
+        <v>62.05</v>
+      </c>
+      <c r="AH6">
+        <v>0.5236947791164659</v>
+      </c>
+      <c r="AI6">
+        <v>0.7392290249433107</v>
+      </c>
+      <c r="AJ6">
+        <v>0.5113308611454471</v>
+      </c>
+      <c r="AK6">
+        <v>0.7295708406819518</v>
+      </c>
+      <c r="AL6">
+        <v>4.57</v>
+      </c>
+      <c r="AM6">
+        <v>4.492</v>
+      </c>
+      <c r="AN6">
+        <v>-75.11520737327189</v>
+      </c>
+      <c r="AO6">
+        <v>-0.9671772428884026</v>
+      </c>
+      <c r="AP6">
+        <v>-71.48617511520737</v>
+      </c>
+      <c r="AQ6">
+        <v>-0.9839715048975957</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Crescera Capital Acquisition Corp. (NasdaqGM:CREC)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K7">
+        <v>14.8</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>-0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>-0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="V7">
+        <v>0.0025054704595186</v>
+      </c>
+      <c r="W7">
+        <v>14800</v>
+      </c>
+      <c r="X7">
+        <v>0.1020284006153536</v>
+      </c>
+      <c r="Y7">
+        <v>14799.89797159938</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>-4.244604316546762</v>
+      </c>
+      <c r="AB7">
+        <v>0.1020068361568974</v>
+      </c>
+      <c r="AC7">
+        <v>-4.34661115270366</v>
+      </c>
+      <c r="AD7">
+        <v>0.152</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0.152</v>
+      </c>
+      <c r="AG7">
+        <v>-0.535</v>
+      </c>
+      <c r="AH7">
+        <v>0.0005540327754126087</v>
+      </c>
+      <c r="AI7">
+        <v>-0.0194672131147541</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.001954944914402646</v>
+      </c>
+      <c r="AK7">
+        <v>0.06297822248381402</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/brazil/brazil_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>1.565</v>
+        <v>0.2276</v>
       </c>
       <c r="E2">
-        <v>-0.278755</v>
+        <v>0.0141</v>
       </c>
       <c r="G2">
-        <v>0.2957854774376472</v>
+        <v>0.2090136471357359</v>
       </c>
       <c r="H2">
-        <v>0.2516699505021865</v>
+        <v>0.1632426248263463</v>
       </c>
       <c r="I2">
-        <v>0.1658417031092316</v>
+        <v>0.1878728446514668</v>
       </c>
       <c r="J2">
-        <v>0.1331549172322448</v>
+        <v>0.1522879554238348</v>
       </c>
       <c r="K2">
-        <v>41.07000000000001</v>
+        <v>33.17</v>
       </c>
       <c r="L2">
-        <v>0.197366524100149</v>
+        <v>0.1355315845386941</v>
       </c>
       <c r="M2">
-        <v>70</v>
+        <v>37.53328</v>
       </c>
       <c r="N2">
-        <v>0.07892036934732855</v>
+        <v>0.05406228214213695</v>
       </c>
       <c r="O2">
-        <v>1.704407109812515</v>
+        <v>1.131542960506482</v>
       </c>
       <c r="P2">
-        <v>55.90000000000001</v>
+        <v>37.53328</v>
       </c>
       <c r="Q2">
-        <v>0.06302355209308094</v>
+        <v>0.05406228214213695</v>
       </c>
       <c r="R2">
-        <v>1.36109082055028</v>
+        <v>1.131542960506482</v>
       </c>
       <c r="S2">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.2014285714285715</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>29.547</v>
+        <v>48.82</v>
       </c>
       <c r="V2">
-        <v>0.03331228790150738</v>
+        <v>0.07031947685305218</v>
       </c>
       <c r="W2">
-        <v>0.05925925925925925</v>
+        <v>0.1169089485299352</v>
       </c>
       <c r="X2">
-        <v>0.106024237166538</v>
+        <v>0.09488578010905988</v>
       </c>
       <c r="Y2">
-        <v>-0.04676497790727877</v>
+        <v>0.02202316842087534</v>
       </c>
       <c r="Z2">
-        <v>0.6045279313460326</v>
+        <v>0.6702634605904584</v>
       </c>
       <c r="AA2">
-        <v>0.03451077701552085</v>
+        <v>0.09099880282463015</v>
       </c>
       <c r="AB2">
-        <v>0.1020323325789546</v>
+        <v>0.08493623590288926</v>
       </c>
       <c r="AC2">
-        <v>-0.06759379037281943</v>
+        <v>0.006062566921740883</v>
       </c>
       <c r="AD2">
-        <v>135.352</v>
+        <v>154.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>135.352</v>
+        <v>154.2</v>
       </c>
       <c r="AG2">
-        <v>105.805</v>
+        <v>105.38</v>
       </c>
       <c r="AH2">
-        <v>0.1323966421538419</v>
+        <v>0.1817410367017891</v>
       </c>
       <c r="AI2">
-        <v>0.2957272576317698</v>
+        <v>0.3120825743776564</v>
       </c>
       <c r="AJ2">
-        <v>0.1065750044068394</v>
+        <v>0.1317843029363214</v>
       </c>
       <c r="AK2">
-        <v>0.2471242219341578</v>
+        <v>0.2366600790513835</v>
       </c>
       <c r="AL2">
-        <v>9.449999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="AM2">
-        <v>8.202</v>
+        <v>-11.155</v>
       </c>
       <c r="AN2">
-        <v>3.711120859837683</v>
+        <v>3.223244147157191</v>
       </c>
       <c r="AO2">
-        <v>3.651851851851852</v>
+        <v>5.069459757442116</v>
       </c>
       <c r="AP2">
-        <v>2.900992542224172</v>
+        <v>2.202759197324415</v>
       </c>
       <c r="AQ2">
-        <v>4.207510363326018</v>
+        <v>-4.121918422232183</v>
       </c>
     </row>
     <row r="3">
@@ -722,115 +722,115 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.5791458607095927</v>
+        <v>0.4070521541950112</v>
       </c>
       <c r="H3">
-        <v>0.5795006570302235</v>
+        <v>0.4058956916099773</v>
       </c>
       <c r="I3">
-        <v>0.4467805519053877</v>
+        <v>0.4648526077097506</v>
       </c>
       <c r="J3">
-        <v>0.3709940161379655</v>
+        <v>0.3729228009611805</v>
       </c>
       <c r="K3">
-        <v>40.2</v>
+        <v>43</v>
       </c>
       <c r="L3">
-        <v>0.5282522996057819</v>
+        <v>0.4875283446712018</v>
       </c>
       <c r="M3">
-        <v>51.8</v>
+        <v>37.51439999999999</v>
       </c>
       <c r="N3">
-        <v>0.1035378772736358</v>
+        <v>0.06359450754365147</v>
       </c>
       <c r="O3">
-        <v>1.288557213930348</v>
+        <v>0.8724279069767441</v>
       </c>
       <c r="P3">
-        <v>37.7</v>
+        <v>37.51439999999999</v>
       </c>
       <c r="Q3">
-        <v>0.07535478712772337</v>
+        <v>0.06359450754365147</v>
       </c>
       <c r="R3">
-        <v>0.9378109452736318</v>
+        <v>0.8724279069767441</v>
       </c>
       <c r="S3">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.2722007722007722</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>18</v>
+        <v>36.9</v>
       </c>
       <c r="V3">
-        <v>0.03597841295222867</v>
+        <v>0.06255297508052213</v>
       </c>
       <c r="W3">
-        <v>0.1521574564723694</v>
+        <v>0.168363351605325</v>
       </c>
       <c r="X3">
-        <v>0.106024237166538</v>
+        <v>0.08739580560957499</v>
       </c>
       <c r="Y3">
-        <v>0.04613321930583142</v>
+        <v>0.08096754599574998</v>
       </c>
       <c r="Z3">
-        <v>0.2890239270793771</v>
+        <v>0.3450704225352113</v>
       </c>
       <c r="AA3">
-        <v>0.1072261474671446</v>
+        <v>0.128684628500689</v>
       </c>
       <c r="AB3">
-        <v>0.1020323325789546</v>
+        <v>0.08455435279752592</v>
       </c>
       <c r="AC3">
-        <v>0.005193814888190026</v>
+        <v>0.04413027570316312</v>
       </c>
       <c r="AD3">
-        <v>48.2</v>
+        <v>50.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>48.2</v>
+        <v>50.5</v>
       </c>
       <c r="AG3">
-        <v>30.2</v>
+        <v>13.6</v>
       </c>
       <c r="AH3">
-        <v>0.0878760255241568</v>
+        <v>0.07885696439725172</v>
       </c>
       <c r="AI3">
-        <v>0.1586048042119118</v>
+        <v>0.1591052299936988</v>
       </c>
       <c r="AJ3">
-        <v>0.05692742695570217</v>
+        <v>0.02253521126760564</v>
       </c>
       <c r="AK3">
-        <v>0.105631339629241</v>
+        <v>0.04848484848484849</v>
       </c>
       <c r="AL3">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="AM3">
-        <v>2.25</v>
+        <v>-16.87</v>
       </c>
       <c r="AN3">
-        <v>1.389048991354467</v>
+        <v>1.191037735849057</v>
       </c>
       <c r="AO3">
-        <v>15.11111111111111</v>
+        <v>20.19704433497537</v>
       </c>
       <c r="AP3">
-        <v>0.8703170028818444</v>
+        <v>0.3207547169811321</v>
       </c>
       <c r="AQ3">
-        <v>15.11111111111111</v>
+        <v>-2.430349733254298</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Investimentos Bemge S.A. (BOVESPA:FIGE3)</t>
+          <t>Ideiasnet S.A. (BOVESPA:PDTC3)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -849,107 +849,113 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="E4">
-        <v>0.00049</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.1941558441558441</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I4">
-        <v>0.9266503667481663</v>
+        <v>0.0638961038961039</v>
       </c>
       <c r="J4">
-        <v>0.6259168704156479</v>
+        <v>0.06007022607022607</v>
       </c>
       <c r="K4">
-        <v>2.56</v>
+        <v>4.57</v>
       </c>
       <c r="L4">
-        <v>0.6259168704156479</v>
+        <v>0.05935064935064936</v>
       </c>
       <c r="M4">
-        <v>18.2</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>2.469470827679783</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>7.109375</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>18.2</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>2.469470827679783</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>7.109375</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>0</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.1950592885375494</v>
       </c>
       <c r="W4">
-        <v>0.05925925925925925</v>
+        <v>0.1896265560165975</v>
       </c>
       <c r="X4">
-        <v>0.1020052760592112</v>
+        <v>0.1023757546085447</v>
       </c>
       <c r="Y4">
-        <v>-0.04274601679995191</v>
+        <v>0.08725080140805276</v>
       </c>
       <c r="Z4">
-        <v>0.09467592592592591</v>
+        <v>1.91589947748196</v>
       </c>
       <c r="AA4">
-        <v>0.05925925925925925</v>
+        <v>0.1150885147401694</v>
       </c>
       <c r="AB4">
-        <v>0.1020052760592112</v>
+        <v>0.08507554333781597</v>
       </c>
       <c r="AC4">
-        <v>-0.04274601679995191</v>
+        <v>0.0300129714023534</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>29.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>29.3</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>19.43</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.3667083854818523</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.4883333333333333</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>0.2774525203484221</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>0.3875922601236785</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1.723</v>
+      </c>
+      <c r="AN4">
+        <v>7.094430992736078</v>
+      </c>
+      <c r="AO4">
+        <v>1.991902834008097</v>
+      </c>
+      <c r="AP4">
+        <v>4.704600484261501</v>
+      </c>
+      <c r="AQ4">
+        <v>2.8554846198491</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Padtec Holding S.A. (BOVESPA:PDTC3)</t>
+          <t>Investimentos Bemge S.A. (BOVESPA:FIGE3)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,118 +975,109 @@
         </is>
       </c>
       <c r="D5">
-        <v>2.467</v>
+        <v>-0.07980000000000001</v>
       </c>
       <c r="E5">
-        <v>-0.5579999999999999</v>
+        <v>0.0141</v>
       </c>
       <c r="G5">
-        <v>0.2042296072507553</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0.06978851963746223</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0.02613293051359517</v>
+        <v>0.934010152284264</v>
       </c>
       <c r="J5">
-        <v>0.01329342619177918</v>
+        <v>0.467005076142132</v>
       </c>
       <c r="K5">
-        <v>0.41</v>
+        <v>1.8</v>
       </c>
       <c r="L5">
-        <v>0.006193353474320241</v>
+        <v>0.4568527918781726</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.01888</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.002083885209713024</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.01048888888888889</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>0.01888</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.002083885209713024</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.01048888888888889</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>7.71</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>0.1683406113537118</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>0.01708333333333333</v>
+        <v>0.06545454545454546</v>
       </c>
       <c r="X5">
-        <v>0.121861116931262</v>
+        <v>0.08479692846796255</v>
       </c>
       <c r="Y5">
-        <v>-0.1047777835979287</v>
+        <v>-0.01934238301341709</v>
       </c>
       <c r="Z5">
-        <v>2.596078431372549</v>
+        <v>0.1432727272727273</v>
       </c>
       <c r="AA5">
-        <v>0.03451077701552085</v>
+        <v>0.06690909090909092</v>
       </c>
       <c r="AB5">
-        <v>0.1021045673883403</v>
+        <v>0.08479692846796255</v>
       </c>
       <c r="AC5">
-        <v>-0.06759379037281943</v>
+        <v>-0.01788783755887163</v>
       </c>
       <c r="AD5">
-        <v>21.8</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>21.8</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>14.09</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>0.3224852071005918</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.4749455337690631</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0.2352646518617465</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>0.3689447499345379</v>
+        <v>0</v>
       </c>
       <c r="AL5">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>1.46</v>
-      </c>
-      <c r="AN5">
-        <v>8.257575757575758</v>
-      </c>
-      <c r="AO5">
-        <v>0.6577946768060837</v>
-      </c>
-      <c r="AP5">
-        <v>5.337121212121212</v>
-      </c>
-      <c r="AQ5">
-        <v>1.184931506849315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1100,25 +1097,25 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.6629999999999999</v>
+        <v>0.535</v>
       </c>
       <c r="G6">
-        <v>0.06413290113452187</v>
+        <v>0.003994708994708994</v>
       </c>
       <c r="H6">
-        <v>0.05915721231766612</v>
+        <v>0.003994708994708994</v>
       </c>
       <c r="I6">
-        <v>-0.07163695299837924</v>
+        <v>-0.04788359788359789</v>
       </c>
       <c r="J6">
-        <v>-0.07163695299837924</v>
+        <v>-0.04788359788359789</v>
       </c>
       <c r="K6">
-        <v>-16.9</v>
+        <v>-16.2</v>
       </c>
       <c r="L6">
-        <v>-0.2739059967585089</v>
+        <v>-0.2142857142857143</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1142,171 +1139,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>3.15</v>
+        <v>2.05</v>
       </c>
       <c r="V6">
-        <v>0.05311973018549747</v>
+        <v>0.04586129753914988</v>
       </c>
       <c r="W6">
-        <v>-0.6425855513307984</v>
+        <v>-0.8265306122448979</v>
       </c>
       <c r="X6">
-        <v>0.1478712025243035</v>
+        <v>0.1353256348547821</v>
       </c>
       <c r="Y6">
-        <v>-0.7904567538551019</v>
+        <v>-0.9618562470996799</v>
       </c>
       <c r="Z6">
-        <v>5.107615894039733</v>
+        <v>1.806451612903225</v>
       </c>
       <c r="AA6">
-        <v>-0.3658940397350992</v>
+        <v>-0.08649940262843488</v>
       </c>
       <c r="AB6">
-        <v>0.102166518651217</v>
+        <v>0.08527154692629076</v>
       </c>
       <c r="AC6">
-        <v>-0.4680605583863162</v>
+        <v>-0.1717709495547256</v>
       </c>
       <c r="AD6">
-        <v>65.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>65.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AG6">
-        <v>62.05</v>
+        <v>72.35000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.5236947791164659</v>
+        <v>0.6246851385390428</v>
       </c>
       <c r="AI6">
-        <v>0.7392290249433107</v>
+        <v>0.8742655699177438</v>
       </c>
       <c r="AJ6">
-        <v>0.5113308611454471</v>
+        <v>0.6181119179837676</v>
       </c>
       <c r="AK6">
-        <v>0.7295708406819518</v>
+        <v>0.8711619506321493</v>
       </c>
       <c r="AL6">
         <v>4.57</v>
       </c>
       <c r="AM6">
-        <v>4.492</v>
+        <v>3.992</v>
       </c>
       <c r="AN6">
-        <v>-75.11520737327189</v>
+        <v>56.79389312977099</v>
       </c>
       <c r="AO6">
-        <v>-0.9671772428884026</v>
+        <v>-0.7921225382932165</v>
       </c>
       <c r="AP6">
-        <v>-71.48617511520737</v>
+        <v>55.22900763358779</v>
       </c>
       <c r="AQ6">
-        <v>-0.9839715048975957</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Crescera Capital Acquisition Corp. (NasdaqGM:CREC)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K7">
-        <v>14.8</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>-0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>-0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0.6870000000000001</v>
-      </c>
-      <c r="V7">
-        <v>0.0025054704595186</v>
-      </c>
-      <c r="W7">
-        <v>14800</v>
-      </c>
-      <c r="X7">
-        <v>0.1020284006153536</v>
-      </c>
-      <c r="Y7">
-        <v>14799.89797159938</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>-4.244604316546762</v>
-      </c>
-      <c r="AB7">
-        <v>0.1020068361568974</v>
-      </c>
-      <c r="AC7">
-        <v>-4.34661115270366</v>
-      </c>
-      <c r="AD7">
-        <v>0.152</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0.152</v>
-      </c>
-      <c r="AG7">
-        <v>-0.535</v>
-      </c>
-      <c r="AH7">
-        <v>0.0005540327754126087</v>
-      </c>
-      <c r="AI7">
-        <v>-0.0194672131147541</v>
-      </c>
-      <c r="AJ7">
-        <v>-0.001954944914402646</v>
-      </c>
-      <c r="AK7">
-        <v>0.06297822248381402</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
+        <v>-0.906813627254509</v>
       </c>
     </row>
   </sheetData>
